--- a/Configs/GameConfig/Datas/__tables__.xlsx
+++ b/Configs/GameConfig/Datas/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="42">
   <si>
     <t>##var</t>
   </si>
@@ -137,13 +137,22 @@
     <t>界面组.xlsx</t>
   </si>
   <si>
-    <t>TbLocalizationConfig</t>
-  </si>
-  <si>
-    <t>LocalizationConfig</t>
-  </si>
-  <si>
-    <t>本地化.xlsx</t>
+    <t>Entity.TbEntityGroupConfig</t>
+  </si>
+  <si>
+    <t>EntityGroupConfig</t>
+  </si>
+  <si>
+    <t>实体组.xlsx</t>
+  </si>
+  <si>
+    <t>Entity.TbEntityConfig</t>
+  </si>
+  <si>
+    <t>EntityConfig</t>
+  </si>
+  <si>
+    <t>实体.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1085,8 +1094,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="6"/>
+  <dimension ref="A1:K8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
     <col min="2" max="2" width="20.3833333333333" customWidth="1"/>
     <col min="3" max="3" width="15.575" customWidth="1"/>
@@ -1241,6 +1250,20 @@
         <v>38</v>
       </c>
     </row>
+    <row r="8" spans="1:11">
+      <c r="B8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" t="s">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Configs/GameConfig/Datas/__tables__.xlsx
+++ b/Configs/GameConfig/Datas/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="45">
   <si>
     <t>##var</t>
   </si>
@@ -153,6 +153,15 @@
   </si>
   <si>
     <t>实体.xlsx</t>
+  </si>
+  <si>
+    <t>Sound.TbSoundConfig</t>
+  </si>
+  <si>
+    <t>SoundConfig</t>
+  </si>
+  <si>
+    <t>声音组.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1094,8 +1103,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7"/>
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="20.3833333333333" customWidth="1"/>
     <col min="3" max="3" width="15.575" customWidth="1"/>
@@ -1264,6 +1273,20 @@
         <v>41</v>
       </c>
     </row>
+    <row r="9" spans="1:11">
+      <c r="B9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" t="s">
+        <v>44</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Configs/GameConfig/Datas/__tables__.xlsx
+++ b/Configs/GameConfig/Datas/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="42">
   <si>
     <t>##var</t>
   </si>
@@ -108,15 +108,6 @@
   </si>
   <si>
     <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
-  </si>
-  <si>
-    <t>item.TbItem</t>
-  </si>
-  <si>
-    <t>Item</t>
-  </si>
-  <si>
-    <t>item.xlsx</t>
   </si>
   <si>
     <t>TbUIFormConfig</t>
@@ -1103,8 +1094,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <dimension ref="A1:K8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
     <col min="2" max="2" width="20.3833333333333" customWidth="1"/>
     <col min="3" max="3" width="15.575" customWidth="1"/>
@@ -1273,20 +1264,6 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
-      <c r="B9" t="s">
-        <v>42</v>
-      </c>
-      <c r="C9" t="s">
-        <v>43</v>
-      </c>
-      <c r="D9" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9" t="s">
-        <v>44</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Configs/GameConfig/Datas/__tables__.xlsx
+++ b/Configs/GameConfig/Datas/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="45">
   <si>
     <t>##var</t>
   </si>
@@ -153,6 +153,15 @@
   </si>
   <si>
     <t>声音组.xlsx</t>
+  </si>
+  <si>
+    <t>Character.TbCharacterConfig</t>
+  </si>
+  <si>
+    <t>CharacterConfig</t>
+  </si>
+  <si>
+    <t>角色.xlsx</t>
   </si>
 </sst>
 </file>
@@ -333,6 +342,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -364,12 +379,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -644,7 +653,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -668,16 +677,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -689,13 +698,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -768,11 +777,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1094,8 +1109,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7"/>
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="20.3833333333333" customWidth="1"/>
     <col min="3" max="3" width="15.575" customWidth="1"/>
@@ -1194,74 +1209,88 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
-      <c r="B4" t="s">
+    <row r="4" s="2" customFormat="1" spans="1:11">
+      <c r="B4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D4" t="b">
+      <c r="D4" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
-      <c r="B5" t="s">
+    <row r="5" s="2" customFormat="1" spans="1:11">
+      <c r="B5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D5" t="b">
+      <c r="D5" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
-      <c r="B6" t="s">
+    <row r="6" s="2" customFormat="1" spans="1:11">
+      <c r="B6" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D6" t="b">
+      <c r="D6" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
-      <c r="B7" t="s">
+    <row r="7" s="2" customFormat="1" spans="1:11">
+      <c r="B7" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D7" t="b">
+      <c r="D7" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
-      <c r="B8" t="s">
+    <row r="8" s="2" customFormat="1" spans="1:11">
+      <c r="B8" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D8" t="b">
+      <c r="D8" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="3" t="s">
         <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="B9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/__tables__.xlsx
+++ b/Configs/GameConfig/Datas/__tables__.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12790"/>
+    <workbookView windowWidth="27930" windowHeight="12975"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
   <si>
     <t>##var</t>
   </si>
@@ -110,7 +110,7 @@
     <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
   </si>
   <si>
-    <t>TbUIFormConfig</t>
+    <t>UI.TbUIFormConfig</t>
   </si>
   <si>
     <t>UIFormConfig</t>
@@ -119,22 +119,13 @@
     <t>界面UI.xlsx</t>
   </si>
   <si>
-    <t>TbUIGroupConfig</t>
-  </si>
-  <si>
-    <t>UIGroupConfig</t>
-  </si>
-  <si>
-    <t>界面组.xlsx</t>
-  </si>
-  <si>
-    <t>Entity.TbEntityGroupConfig</t>
-  </si>
-  <si>
-    <t>EntityGroupConfig</t>
-  </si>
-  <si>
-    <t>实体组.xlsx</t>
+    <t>Character.TbCharacterConfig</t>
+  </si>
+  <si>
+    <t>CharacterConfig</t>
+  </si>
+  <si>
+    <t>角色.xlsx</t>
   </si>
   <si>
     <t>Entity.TbEntityConfig</t>
@@ -144,24 +135,6 @@
   </si>
   <si>
     <t>实体.xlsx</t>
-  </si>
-  <si>
-    <t>Sound.TbSoundConfig</t>
-  </si>
-  <si>
-    <t>SoundConfig</t>
-  </si>
-  <si>
-    <t>声音组.xlsx</t>
-  </si>
-  <si>
-    <t>Character.TbCharacterConfig</t>
-  </si>
-  <si>
-    <t>CharacterConfig</t>
-  </si>
-  <si>
-    <t>角色.xlsx</t>
   </si>
 </sst>
 </file>
@@ -169,10 +142,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -342,43 +315,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -632,19 +605,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -653,7 +626,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -677,16 +650,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -698,13 +671,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -777,17 +750,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="22" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1109,8 +1079,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5"/>
   <cols>
     <col min="2" max="2" width="20.3833333333333" customWidth="1"/>
     <col min="3" max="3" width="15.575" customWidth="1"/>
@@ -1210,87 +1180,45 @@
       </c>
     </row>
     <row r="4" s="2" customFormat="1" spans="1:11">
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D4" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="5" s="2" customFormat="1" spans="1:11">
-      <c r="B5" s="3" t="s">
+    <row r="5" spans="1:11">
+      <c r="B5" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" t="s">
         <v>31</v>
       </c>
-      <c r="D5" s="2" t="b">
+      <c r="D5" t="b">
         <v>1</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="6" s="2" customFormat="1" spans="1:11">
-      <c r="B6" s="3" t="s">
+    <row r="6" spans="1:11">
+      <c r="B6" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="2" t="b">
+      <c r="D6" t="b">
         <v>1</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" t="s">
         <v>35</v>
-      </c>
-    </row>
-    <row r="7" s="2" customFormat="1" spans="1:11">
-      <c r="B7" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D7" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="8" s="2" customFormat="1" spans="1:11">
-      <c r="B8" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D8" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="B9" t="s">
-        <v>42</v>
-      </c>
-      <c r="C9" t="s">
-        <v>43</v>
-      </c>
-      <c r="D9" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9" t="s">
-        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/__tables__.xlsx
+++ b/Configs/GameConfig/Datas/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
   <si>
     <t>##var</t>
   </si>
@@ -135,6 +135,15 @@
   </si>
   <si>
     <t>实体.xlsx</t>
+  </si>
+  <si>
+    <t>Level.TbLevelConfig</t>
+  </si>
+  <si>
+    <t>LevelConfig</t>
+  </si>
+  <si>
+    <t>关卡.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1079,8 +1088,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5"/>
+  <dimension ref="A1:K7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6"/>
   <cols>
     <col min="2" max="2" width="20.3833333333333" customWidth="1"/>
     <col min="3" max="3" width="15.575" customWidth="1"/>
@@ -1221,6 +1230,20 @@
         <v>35</v>
       </c>
     </row>
+    <row r="7" spans="1:11">
+      <c r="B7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" t="s">
+        <v>38</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
